--- a/LTD_MAIN_CPU2/docs/LTD故障代码表.xlsx
+++ b/LTD_MAIN_CPU2/docs/LTD故障代码表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32565" windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="369">
   <si>
     <t>故障类型</t>
   </si>
@@ -796,6 +796,12 @@
     <t>数据校验</t>
   </si>
   <si>
+    <t>分布测量上限</t>
+  </si>
+  <si>
+    <t>分布测量下限</t>
+  </si>
+  <si>
     <t>结构体</t>
   </si>
   <si>
@@ -1127,6 +1133,9 @@
   </si>
   <si>
     <t>密度分布测量数据</t>
+  </si>
+  <si>
+    <t>数据更新标志位</t>
   </si>
 </sst>
 </file>
@@ -2404,7 +2413,7 @@
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
     </row>
-    <row r="2" spans="4:17">
+    <row r="2" spans="2:17">
       <c r="D2" s="8"/>
       <c r="H2">
         <v>1</v>
@@ -2437,7 +2446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:6">
+    <row r="3" spans="2:17">
       <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
@@ -2454,7 +2463,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
+    <row r="4" spans="2:17">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8">
@@ -2467,7 +2476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:17">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8">
@@ -2480,7 +2489,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:17">
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8">
@@ -2493,7 +2502,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="2:17">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8">
@@ -2506,7 +2515,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:17">
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8">
@@ -2519,7 +2528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" spans="2:17">
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8">
@@ -2532,7 +2541,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6">
+    <row r="10" spans="2:17">
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8">
@@ -2545,7 +2554,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="2:6">
+    <row r="11" spans="2:17">
       <c r="B11" s="8" t="s">
         <v>23</v>
       </c>
@@ -2562,7 +2571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:6">
+    <row r="12" spans="2:17">
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8">
@@ -2575,7 +2584,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="2:6">
+    <row r="13" spans="2:17">
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8">
@@ -2588,7 +2597,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="2:6">
+    <row r="14" spans="2:17">
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8">
@@ -2601,7 +2610,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:6">
+    <row r="15" spans="2:17">
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8">
@@ -2614,7 +2623,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="2:17">
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8">
@@ -3119,16 +3128,16 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="4:4">
+    <row r="53" spans="2:6">
       <c r="D53" s="8"/>
     </row>
-    <row r="54" spans="4:4">
+    <row r="54" spans="2:6">
       <c r="D54" s="8"/>
     </row>
-    <row r="55" spans="4:4">
+    <row r="55" spans="2:6">
       <c r="D55" s="8"/>
     </row>
-    <row r="56" spans="4:4">
+    <row r="56" spans="2:6">
       <c r="D56" s="8"/>
     </row>
   </sheetData>
@@ -3180,7 +3189,7 @@
     <col min="4" max="4" width="35.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="18.75" spans="1:1">
+    <row r="2" ht="18.75" spans="1:4">
       <c r="A2" s="3" t="s">
         <v>113</v>
       </c>
@@ -3298,7 +3307,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" ht="18.75" spans="1:1">
+    <row r="13" ht="18.75" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>141</v>
       </c>
@@ -3374,7 +3383,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="21" ht="18.75" spans="1:1">
+    <row r="21" ht="18.75" spans="1:4">
       <c r="A21" s="3" t="s">
         <v>154</v>
       </c>
@@ -3408,7 +3417,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="26" ht="18.75" spans="1:1">
+    <row r="26" ht="18.75" spans="1:4">
       <c r="A26" s="3" t="s">
         <v>158</v>
       </c>
@@ -3456,7 +3465,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="32" ht="18.75" spans="1:1">
+    <row r="32" ht="18.75" spans="1:4">
       <c r="A32" s="3" t="s">
         <v>165</v>
       </c>
@@ -3616,7 +3625,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="46" ht="18.75" spans="1:1">
+    <row r="46" ht="18.75" spans="1:4">
       <c r="A46" s="3" t="s">
         <v>194</v>
       </c>
@@ -3664,7 +3673,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="52" ht="18.75" spans="1:1">
+    <row r="52" ht="18.75" spans="1:4">
       <c r="A52" s="3" t="s">
         <v>201</v>
       </c>
@@ -3740,7 +3749,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="60" ht="18.75" spans="1:1">
+    <row r="60" ht="18.75" spans="1:4">
       <c r="A60" s="3" t="s">
         <v>213</v>
       </c>
@@ -3788,7 +3797,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" ht="18.75" spans="1:1">
+    <row r="66" ht="18.75" spans="1:4">
       <c r="A66" s="3" t="s">
         <v>220</v>
       </c>
@@ -3836,7 +3845,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="72" ht="18.75" spans="1:1">
+    <row r="72" ht="18.75" spans="1:4">
       <c r="A72" s="3" t="s">
         <v>226</v>
       </c>
@@ -3982,7 +3991,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="85" ht="18.75" spans="1:1">
+    <row r="85" ht="18.75" spans="1:4">
       <c r="A85" s="3" t="s">
         <v>251</v>
       </c>
@@ -4016,11 +4025,18 @@
         <v>254</v>
       </c>
     </row>
-    <row r="90" ht="22.5" spans="1:1">
+    <row r="90" ht="22.5" spans="1:4">
       <c r="A90" s="6"/>
     </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="7"/>
+    <row r="95" spans="1:4">
+      <c r="A95" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="7"/>
@@ -4046,7 +4062,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="26" style="1" customWidth="1"/>
@@ -4058,66 +4074,66 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>119</v>
@@ -4128,374 +4144,374 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="D24" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>123</v>
@@ -4506,254 +4522,259 @@
     </row>
     <row r="33" s="1" customFormat="1" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="D40" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:4">
       <c r="A45" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:4">
       <c r="A46" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:4">
       <c r="A48" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:4">
       <c r="A50" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/LTD_MAIN_CPU2/docs/LTD故障代码表.xlsx
+++ b/LTD_MAIN_CPU2/docs/LTD故障代码表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="370">
   <si>
     <t>故障类型</t>
   </si>
@@ -1136,6 +1136,9 @@
   </si>
   <si>
     <t>数据更新标志位</t>
+  </si>
+  <si>
+    <t>称重不检测区域</t>
   </si>
 </sst>
 </file>
@@ -4062,7 +4065,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="26" style="1" customWidth="1"/>
@@ -4777,6 +4780,11 @@
         <v>368</v>
       </c>
     </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/LTD_MAIN_CPU2/docs/LTD故障代码表.xlsx
+++ b/LTD_MAIN_CPU2/docs/LTD故障代码表.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
     <sheet name="设备参数" sheetId="4" r:id="rId2"/>
     <sheet name="测量结果" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="383">
   <si>
     <t>故障类型</t>
   </si>
@@ -1139,6 +1140,45 @@
   </si>
   <si>
     <t>称重不检测区域</t>
+  </si>
+  <si>
+    <t>罐底检测角度阈值</t>
+  </si>
+  <si>
+    <t>罐底检测称重阈值</t>
+  </si>
+  <si>
+    <t>罐底检测方式</t>
+  </si>
+  <si>
+    <t>液位传感器距离差</t>
+  </si>
+  <si>
+    <t>电机运行速度</t>
+  </si>
+  <si>
+    <t>水位罐高</t>
+  </si>
+  <si>
+    <t>电机步进数</t>
+  </si>
+  <si>
+    <t>电机距离</t>
+  </si>
+  <si>
+    <t>电机转股圈数</t>
+  </si>
+  <si>
+    <t>传感器角度X</t>
+  </si>
+  <si>
+    <t>传感器角度Y</t>
+  </si>
+  <si>
+    <t>报错后是否回零点</t>
+  </si>
+  <si>
+    <t>报错后是否停止测量</t>
   </si>
 </sst>
 </file>
@@ -1831,6 +1871,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1842,9 +1885,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3193,846 +3233,846 @@
   </cols>
   <sheetData>
     <row r="2" ht="18.75" spans="1:4">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="3" ht="14.25"/>
     <row r="4" ht="14.25" spans="1:4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:4">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:4">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:4">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:4">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="9" ht="26.25" spans="1:4">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:4">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:4">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="13" ht="18.75" spans="1:4">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="14" ht="14.25"/>
     <row r="15" ht="14.25" spans="1:4">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:4">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="6" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="1:4">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="18" ht="14.25" spans="1:4">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="1:4">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="B19" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="6" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="21" ht="18.75" spans="1:4">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="22" ht="14.25"/>
     <row r="23" ht="14.25" spans="1:4">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="24" ht="14.25" spans="1:4">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="B24" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="6" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="26" ht="18.75" spans="1:4">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="27" ht="14.25"/>
     <row r="28" ht="14.25" spans="1:4">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="29" ht="14.25" spans="1:4">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" s="5" t="s">
+      <c r="B29" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="6" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="30" ht="14.25" spans="1:4">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C30" s="5" t="s">
+      <c r="B30" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="6" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="32" ht="18.75" spans="1:4">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="33" ht="14.25"/>
     <row r="34" ht="14.25" spans="1:4">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="35" ht="14.25" spans="1:4">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C35" s="5" t="s">
+      <c r="B35" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="6" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="36" ht="14.25" spans="1:4">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C36" s="5" t="s">
+      <c r="B36" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="6" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="37" ht="14.25" spans="1:4">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C37" s="5" t="s">
+      <c r="B37" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="6" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="38" ht="14.25" spans="1:4">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C38" s="5" t="s">
+      <c r="B38" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="6" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="39" ht="14.25" spans="1:4">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C39" s="5" t="s">
+      <c r="B39" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="6" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="40" ht="14.25" spans="1:4">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C40" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="6" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:4">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C41" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="6" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="42" ht="26.25" spans="1:4">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C42" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="6" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="43" ht="26.25" spans="1:4">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C43" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="6" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="44" ht="14.25" spans="1:4">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C44" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="6" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="46" ht="18.75" spans="1:4">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="4" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="47" ht="14.25"/>
     <row r="48" ht="14.25" spans="1:4">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="49" ht="14.25" spans="1:4">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C49" s="5" t="s">
+      <c r="B49" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="6" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="50" ht="14.25" spans="1:4">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C50" s="5" t="s">
+      <c r="B50" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="6" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="52" ht="18.75" spans="1:4">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="4" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="53" ht="14.25"/>
     <row r="54" ht="14.25" spans="1:4">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="55" ht="14.25" spans="1:4">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55" s="5" t="s">
+      <c r="B55" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C55" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D55" s="6" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="56" ht="14.25" spans="1:4">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C56" s="5" t="s">
+      <c r="B56" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="6" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="57" ht="14.25" spans="1:4">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C57" s="5" t="s">
+      <c r="B57" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D57" s="6" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="58" ht="14.25" spans="1:4">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C58" s="5" t="s">
+      <c r="B58" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" s="6" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="60" ht="18.75" spans="1:4">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="4" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="61" ht="14.25"/>
     <row r="62" ht="14.25" spans="1:4">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="63" ht="14.25" spans="1:4">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C63" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D63" s="6" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="64" ht="26.25" spans="1:4">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C64" s="5" t="s">
+      <c r="B64" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="6" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="66" ht="18.75" spans="1:4">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="4" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="67" ht="14.25"/>
     <row r="68" ht="14.25" spans="1:4">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="69" ht="14.25" spans="1:4">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C69" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C69" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D69" s="6" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="70" ht="14.25" spans="1:4">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C70" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="D70" s="6" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="72" ht="18.75" spans="1:4">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="4" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="73" ht="14.25"/>
     <row r="74" ht="14.25" spans="1:4">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="75" ht="14.25" spans="1:4">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="B75" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C75" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C75" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="D75" s="6" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="76" ht="14.25" spans="1:4">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C76" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C76" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D76" s="6" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="77" ht="14.25" spans="1:4">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="B77" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C77" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C77" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="D77" s="6" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="78" ht="14.25" spans="1:4">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="B78" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C78" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C78" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D78" s="5" t="s">
+      <c r="D78" s="6" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="79" ht="14.25" spans="1:4">
-      <c r="A79" s="5" t="s">
+      <c r="A79" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B79" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C79" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C79" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="D79" s="6" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="80" ht="14.25" spans="1:4">
-      <c r="A80" s="5" t="s">
+      <c r="A80" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="B80" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C80" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C80" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="D80" s="6" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="81" ht="14.25" spans="1:4">
-      <c r="A81" s="5" t="s">
+      <c r="A81" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="B81" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C81" s="5" t="s">
+      <c r="B81" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C81" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="D81" s="5" t="s">
+      <c r="D81" s="6" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="82" ht="14.25" spans="1:4">
-      <c r="A82" s="5" t="s">
+      <c r="A82" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="B82" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C82" s="5" t="s">
+      <c r="B82" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C82" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D82" s="6" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="83" ht="14.25" spans="1:4">
-      <c r="A83" s="5" t="s">
+      <c r="A83" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="B83" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C83" s="5" t="s">
+      <c r="B83" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C83" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="D83" s="6" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="85" ht="18.75" spans="1:4">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="4" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="86" ht="14.25"/>
     <row r="87" ht="14.25" spans="1:4">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="88" ht="14.25" spans="1:4">
-      <c r="A88" s="5" t="s">
+      <c r="A88" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="B88" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C88" s="5" t="s">
+      <c r="B88" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C88" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D88" s="5" t="s">
+      <c r="D88" s="6" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="90" ht="22.5" spans="1:4">
-      <c r="A90" s="6"/>
+      <c r="A90" s="7"/>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="7" t="s">
+      <c r="A95" s="3" t="s">
         <v>255</v>
       </c>
     </row>
@@ -4042,19 +4082,19 @@
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="7"/>
+      <c r="A97" s="3"/>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="7"/>
+      <c r="A99" s="3"/>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="7"/>
+      <c r="A101" s="3"/>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="7"/>
+      <c r="A103" s="3"/>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="7"/>
+      <c r="A105" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4065,7 +4105,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="26" style="1" customWidth="1"/>
@@ -4785,8 +4825,94 @@
         <v>369</v>
       </c>
     </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/LTD_MAIN_CPU2/docs/LTD故障代码表.xlsx
+++ b/LTD_MAIN_CPU2/docs/LTD故障代码表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="2"/>
+    <workbookView windowWidth="32745" windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="386">
   <si>
     <t>故障类型</t>
   </si>
@@ -1158,6 +1158,15 @@
   </si>
   <si>
     <t>水位罐高</t>
+  </si>
+  <si>
+    <t>水位电容阈值</t>
+  </si>
+  <si>
+    <t>水位滞后阈</t>
+  </si>
+  <si>
+    <t>水位标定值</t>
   </si>
   <si>
     <t>电机步进数</t>
@@ -4854,6 +4863,15 @@
       <c r="A61" s="1" t="s">
         <v>375</v>
       </c>
+      <c r="B61" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="3" t="s">
@@ -4867,37 +4885,37 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
